--- a/data/trans_dic/P32A-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32A-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le ha molestado que le criticasen la forma de beber</t>
+          <t>Población a la que le ha molestado que le criticasen la forma de beber (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,81</t>
+          <t>1,29; 7,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,3; 18,37</t>
+          <t>8,98; 19,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 9,4</t>
+          <t>2,23; 9,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,58</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,73</t>
+          <t>1,66; 12,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 11,1</t>
+          <t>0,88; 10,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,85</t>
+          <t>0,86; 5,12</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,56; 13,64</t>
+          <t>6,43; 13,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 8,08</t>
+          <t>2,37; 8,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 3,48</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,69</t>
+          <t>0,89; 5,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,26</t>
+          <t>0,32; 4,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,96</t>
+          <t>0,83; 4,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,98</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,17</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,8</t>
+          <t>0,68; 3,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,14</t>
+          <t>0,41; 3,31</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,46</t>
+          <t>0,87; 3,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
     </row>
@@ -997,52 +997,52 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 3,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,63</t>
+          <t>1,98; 7,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,37</t>
+          <t>1,74; 5,23</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 3,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,72</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,4; 3,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 5,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,85</t>
+          <t>0,39; 3,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,11</t>
+          <t>0,25; 2,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,89</t>
+          <t>0,54; 2,89</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,66</t>
+          <t>0,0; 4,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,4</t>
+          <t>1,53; 9,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 8,59</t>
+          <t>1,01; 8,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,36</t>
+          <t>0,0; 9,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,67</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,65</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,79</t>
+          <t>1,56; 7,15</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,97</t>
+          <t>0,72; 6,08</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,48</t>
+          <t>0,0; 2,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,34</t>
+          <t>0,47; 4,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,21</t>
+          <t>1,29; 6,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,14</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,04</t>
+          <t>0,57; 6,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,8</t>
+          <t>0,63; 4,05</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,91</t>
+          <t>1,25; 4,75</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,48</t>
+          <t>0,99; 4,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,34</t>
+          <t>2,29; 6,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,23</t>
+          <t>1,05; 4,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,18</t>
+          <t>0,47; 4,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,36</t>
+          <t>0,35; 5,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,22</t>
+          <t>0,82; 3,29</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,5</t>
+          <t>1,9; 4,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,88</t>
+          <t>0,74; 3,65</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,55</t>
+          <t>0,16; 1,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,52</t>
+          <t>0,45; 3,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,45</t>
+          <t>0,0; 1,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,81</t>
+          <t>0,25; 2,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,87</t>
+          <t>0,4; 3,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,58</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,33</t>
+          <t>0,24; 1,39</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,41</t>
+          <t>0,31; 2,26</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,69</t>
+          <t>0,3; 1,75</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,37</t>
+          <t>0,27; 2,11</t>
         </is>
       </c>
     </row>
@@ -1837,22 +1837,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,65</t>
+          <t>0,64; 1,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,41</t>
+          <t>1,88; 3,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,7</t>
+          <t>1,44; 2,77</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,46</t>
+          <t>1,23; 2,5</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1862,37 +1862,37 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,68</t>
+          <t>0,39; 1,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,3</t>
+          <t>0,77; 2,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,4</t>
+          <t>0,59; 2,37</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,23</t>
+          <t>0,55; 1,27</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,6</t>
+          <t>1,46; 2,54</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,24</t>
+          <t>1,31; 2,26</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,18</t>
+          <t>1,1; 2,14</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le ha molestado que le criticasen la forma de beber</t>
+          <t>Población a la que le ha molestado que le criticasen la forma de beber (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1012; 11410</t>
+          <t>1888; 10520</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14554; 32209</t>
+          <t>15737; 33582</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4179; 16802</t>
+          <t>3988; 17257</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 10042</t>
+          <t>0; 7781</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1982</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1200; 11773</t>
+          <t>1825; 13674</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>939; 11784</t>
+          <t>932; 10951</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 1061</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1898; 10651</t>
+          <t>1891; 11244</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18688; 38877</t>
+          <t>18335; 39720</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7285; 23022</t>
+          <t>6751; 23394</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 10938</t>
+          <t>0; 9423</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2045; 10742</t>
+          <t>2042; 11438</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>952; 13179</t>
+          <t>992; 14038</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2226; 13283</t>
+          <t>2227; 13014</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 6857</t>
+          <t>0; 8083</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1909</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 6021</t>
+          <t>0; 5310</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6309</t>
+          <t>0; 6517</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 1509</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2044; 11462</t>
+          <t>2044; 11564</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1878; 14457</t>
+          <t>1901; 15233</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3311; 16501</t>
+          <t>3222; 14435</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 7076</t>
+          <t>0; 7175</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5230</t>
+          <t>0; 6382</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4784</t>
+          <t>0; 4929</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 4988</t>
+          <t>0; 5174</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3549; 12280</t>
+          <t>3672; 13495</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1872</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2078</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1850</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3492</t>
+          <t>0; 3679</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5782</t>
+          <t>0; 5920</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5373</t>
+          <t>0; 4694</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4352</t>
+          <t>0; 4336</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4534; 14781</t>
+          <t>4784; 14396</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5956</t>
+          <t>0; 6883</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5786</t>
+          <t>0; 6646</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6340</t>
+          <t>0; 6311</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6850</t>
+          <t>717; 6770</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4940</t>
+          <t>0; 6755</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1992</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2064</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>422; 4790</t>
+          <t>482; 4560</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>915; 7795</t>
+          <t>927; 8016</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5791</t>
+          <t>0; 6722</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 6955</t>
+          <t>0; 5175</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1814; 8730</t>
+          <t>1623; 8729</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4511</t>
+          <t>0; 4301</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1893; 10768</t>
+          <t>1960; 12087</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>924; 7835</t>
+          <t>919; 7470</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1267</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2009</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5065</t>
+          <t>0; 5187</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 1746</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2375</t>
+          <t>0; 2046</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5266</t>
+          <t>0; 6095</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2183; 12384</t>
+          <t>2837; 13031</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>924; 7675</t>
+          <t>927; 7826</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2437</t>
+          <t>0; 2490</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 10043</t>
+          <t>0; 9495</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6356</t>
+          <t>0; 5423</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>892; 8204</t>
+          <t>885; 8094</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2282; 10243</t>
+          <t>2129; 10340</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1966</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5150</t>
+          <t>0; 5056</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6486</t>
+          <t>0; 7447</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>526; 5825</t>
+          <t>552; 6135</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 8664</t>
+          <t>0; 9724</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 6325</t>
+          <t>0; 7232</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1829; 11193</t>
+          <t>1868; 11930</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3455; 12832</t>
+          <t>3260; 12416</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5726</t>
+          <t>0; 6558</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4032; 17666</t>
+          <t>3914; 17906</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7946; 24062</t>
+          <t>8694; 26238</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2814; 13031</t>
+          <t>3224; 13863</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 1923</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 4963</t>
+          <t>0; 5138</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1116; 10683</t>
+          <t>1209; 10820</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>980; 21419</t>
+          <t>1399; 20734</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 6650</t>
+          <t>0; 5566</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5157; 19506</t>
+          <t>4983; 19922</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>11246; 28603</t>
+          <t>12043; 30497</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5776; 27453</t>
+          <t>5240; 25833</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>771; 7625</t>
+          <t>777; 7497</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2586; 15927</t>
+          <t>2048; 15244</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 6608</t>
+          <t>0; 6573</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>648; 7773</t>
+          <t>694; 7538</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 6818</t>
+          <t>0; 6250</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0; 2085</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1076; 10220</t>
+          <t>1060; 9733</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 4539</t>
+          <t>0; 3826</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1771; 9711</t>
+          <t>1771; 10189</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2062; 16040</t>
+          <t>2070; 15041</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2072; 12206</t>
+          <t>2139; 12603</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1013; 8911</t>
+          <t>1021; 7921</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>12904; 30978</t>
+          <t>11965; 29959</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>37804; 69413</t>
+          <t>38180; 69394</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27273; 54016</t>
+          <t>28847; 55342</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19920; 38761</t>
+          <t>19406; 39309</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>924; 7924</t>
+          <t>920; 7988</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4015; 17596</t>
+          <t>4072; 18124</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8583; 26333</t>
+          <t>8814; 24966</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>6208; 24462</t>
+          <t>6027; 24138</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>15185; 34160</t>
+          <t>15277; 35166</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>44321; 79962</t>
+          <t>45046; 78254</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41469; 70542</t>
+          <t>41155; 71005</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>29711; 56615</t>
+          <t>28537; 55541</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32A-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P32A-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,2</t>
+          <t>1,31; 7,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,98; 19,15</t>
+          <t>8,82; 19,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 9,66</t>
+          <t>2,38; 10,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 4,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 12,47</t>
+          <t>1,11; 10,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 10,32</t>
+          <t>0,88; 10,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,12</t>
+          <t>0,87; 4,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,43; 13,94</t>
+          <t>6,64; 13,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,37; 8,21</t>
+          <t>2,41; 7,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,48</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,0</t>
+          <t>0,9; 5,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,54</t>
+          <t>0,31; 4,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,86</t>
+          <t>0,83; 5,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 2,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 4,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,31</t>
+          <t>0,41; 3,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,9</t>
+          <t>0,89; 4,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,11</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,29</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,98; 7,29</t>
+          <t>2,22; 7,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,33</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,23</t>
+          <t>1,85; 5,54</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,89</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,48</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,81</t>
+          <t>0,34; 3,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,16</t>
+          <t>0,0; 3,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1172,27 +1172,27 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,67</t>
+          <t>0,33; 3,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,17</t>
+          <t>0,25; 2,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,34</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,89</t>
+          <t>0,52; 2,72</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,44</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 9,43</t>
+          <t>1,51; 10,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 8,19</t>
+          <t>1,02; 8,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,59</t>
+          <t>0,0; 8,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,23</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,15</t>
+          <t>1,09; 6,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,08</t>
+          <t>0,73; 6,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 4,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,28</t>
+          <t>0,47; 3,44</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,27</t>
+          <t>1,13; 5,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,22 +1442,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 7,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,36</t>
+          <t>0,56; 6,33</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,63; 4,05</t>
+          <t>0,62; 3,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,75</t>
+          <t>1,33; 4,76</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,54</t>
+          <t>0,98; 4,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,91</t>
+          <t>2,12; 6,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,5</t>
+          <t>1,15; 4,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,37 +1582,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,24</t>
+          <t>0,44; 4,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,35; 5,19</t>
+          <t>2,86; 10,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,32</t>
+          <t>0,0; 1,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,29</t>
+          <t>0,85; 3,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,8</t>
+          <t>1,7; 4,61</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,65</t>
+          <t>2,2; 5,86</t>
         </is>
       </c>
     </row>
@@ -1644,39 +1644,39 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
           <t>0,83%</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -1697,27 +1697,27 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,52</t>
+          <t>0,16; 1,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,37</t>
+          <t>0,45; 3,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,44</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,73</t>
+          <t>0,23; 2,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1727,32 +1727,32 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,69</t>
+          <t>0,37; 3,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,39</t>
+          <t>0,24; 1,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,26</t>
+          <t>0,31; 2,34</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,75</t>
+          <t>0,29; 1,78</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,11</t>
+          <t>0,19; 2,16</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,59</t>
+          <t>0,66; 1,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,41</t>
+          <t>1,92; 3,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,77</t>
+          <t>1,39; 2,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,5</t>
+          <t>1,26; 2,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,89</t>
+          <t>0,1; 0,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,74</t>
+          <t>0,37; 1,65</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,18</t>
+          <t>0,73; 2,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,37</t>
+          <t>1,3; 3,44</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,27</t>
+          <t>0,55; 1,28</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,54</t>
+          <t>1,5; 2,61</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,26</t>
+          <t>1,29; 2,28</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,14</t>
+          <t>1,48; 2,55</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2315</t>
+          <t>1955</t>
         </is>
       </c>
     </row>
@@ -2209,22 +2209,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1888; 10520</t>
+          <t>1909; 10817</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>15737; 33582</t>
+          <t>15459; 34202</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3988; 17257</t>
+          <t>4256; 18240</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7781</t>
+          <t>0; 7099</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1825; 13674</t>
+          <t>1217; 11891</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>932; 10951</t>
+          <t>930; 10747</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,22 +2249,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1891; 11244</t>
+          <t>1911; 10712</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18335; 39720</t>
+          <t>18938; 38736</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6751; 23394</t>
+          <t>6873; 22661</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 9423</t>
+          <t>0; 6339</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1381</t>
         </is>
       </c>
     </row>
@@ -2417,22 +2417,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2042; 11438</t>
+          <t>2057; 12685</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>992; 14038</t>
+          <t>951; 13106</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2227; 13014</t>
+          <t>2228; 13823</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 8083</t>
+          <t>0; 7329</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5310</t>
+          <t>0; 5350</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 6517</t>
+          <t>0; 4510</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2457,22 +2457,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2044; 11564</t>
+          <t>2063; 11540</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1901; 15233</t>
+          <t>1880; 14501</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3222; 14435</t>
+          <t>3294; 14935</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 7175</t>
+          <t>0; 7782</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8448</t>
+          <t>9040</t>
         </is>
       </c>
     </row>
@@ -2625,22 +2625,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6382</t>
+          <t>0; 5845</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4929</t>
+          <t>0; 4571</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5174</t>
+          <t>0; 4763</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3672; 13495</t>
+          <t>4166; 14070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2660,27 +2660,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3679</t>
+          <t>0; 3486</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 5920</t>
+          <t>0; 5302</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4694</t>
+          <t>0; 5815</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4336</t>
+          <t>0; 4860</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4784; 14396</t>
+          <t>5121; 15322</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4285</t>
         </is>
       </c>
     </row>
@@ -2833,27 +2833,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 6883</t>
+          <t>0; 6081</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6646</t>
+          <t>0; 5912</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 6311</t>
+          <t>0; 6383</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>717; 6770</t>
+          <t>692; 7056</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6755</t>
+          <t>0; 4679</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2868,27 +2868,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>482; 4560</t>
+          <t>453; 4719</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>927; 8016</t>
+          <t>915; 7375</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 6722</t>
+          <t>0; 6169</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 5175</t>
+          <t>0; 8242</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1623; 8729</t>
+          <t>1777; 9266</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4301</t>
+          <t>0; 4113</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1960; 12087</t>
+          <t>1935; 13012</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>919; 7470</t>
+          <t>934; 7553</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3066,7 +3066,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5187</t>
+          <t>0; 4528</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -3076,27 +3076,27 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2046</t>
+          <t>0; 2560</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6095</t>
+          <t>0; 4459</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2837; 13031</t>
+          <t>1983; 12258</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>927; 7826</t>
+          <t>933; 8636</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2490</t>
+          <t>0; 2472</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4734</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6966</t>
         </is>
       </c>
     </row>
@@ -3249,22 +3249,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 9495</t>
+          <t>0; 9289</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5423</t>
+          <t>0; 5777</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>885; 8094</t>
+          <t>890; 6510</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2129; 10340</t>
+          <t>1837; 9528</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3274,37 +3274,37 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5056</t>
+          <t>0; 5358</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 7447</t>
+          <t>0; 7793</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>552; 6135</t>
+          <t>546; 6213</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 9724</t>
+          <t>0; 7993</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 7232</t>
+          <t>0; 7231</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1868; 11930</t>
+          <t>1833; 10576</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3260; 12416</t>
+          <t>3484; 12436</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>14753</t>
+          <t>21891</t>
         </is>
       </c>
     </row>
@@ -3457,22 +3457,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6558</t>
+          <t>0; 6446</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3914; 17906</t>
+          <t>3849; 17914</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8694; 26238</t>
+          <t>8047; 25331</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3224; 13863</t>
+          <t>4023; 16433</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3482,37 +3482,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 5138</t>
+          <t>0; 5746</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1209; 10820</t>
+          <t>1117; 10511</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1399; 20734</t>
+          <t>6712; 23831</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5566</t>
+          <t>0; 5687</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4983; 19922</t>
+          <t>5125; 20010</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12043; 30497</t>
+          <t>10826; 29306</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5240; 25833</t>
+          <t>12866; 34251</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>804</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3823</t>
         </is>
       </c>
     </row>
@@ -3665,27 +3665,27 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>777; 7497</t>
+          <t>776; 6969</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2048; 15244</t>
+          <t>2053; 17198</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 6573</t>
+          <t>0; 6814</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>694; 7538</t>
+          <t>725; 8480</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0; 6250</t>
+          <t>0; 7164</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3695,32 +3695,32 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1060; 9733</t>
+          <t>984; 10402</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 3826</t>
+          <t>0; 3821</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1771; 10189</t>
+          <t>1742; 9581</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2070; 15041</t>
+          <t>2034; 15581</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2139; 12603</t>
+          <t>2099; 12824</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1021; 7921</t>
+          <t>804; 9244</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27988</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>19375</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>42084</t>
+          <t>49810</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>11965; 29959</t>
+          <t>12346; 29693</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>38180; 69394</t>
+          <t>39128; 70569</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28847; 55342</t>
+          <t>27913; 53413</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19406; 39309</t>
+          <t>21105; 42024</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>920; 7988</t>
+          <t>924; 8006</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4072; 18124</t>
+          <t>3822; 17226</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8814; 24966</t>
+          <t>8363; 24760</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>6027; 24138</t>
+          <t>11687; 30924</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>15277; 35166</t>
+          <t>15380; 35509</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>45046; 78254</t>
+          <t>46237; 80252</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>41155; 71005</t>
+          <t>40566; 71659</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>28537; 55541</t>
+          <t>37978; 65653</t>
         </is>
       </c>
     </row>
